--- a/jogos_2025-01-15.xlsx
+++ b/jogos_2025-01-15.xlsx
@@ -772,25 +772,25 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Port FC</t>
+          <t>Prachuap</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Khon Kaen United</t>
+          <t>Sukhothai</t>
         </is>
       </c>
       <c r="G3" t="n">
         <v>1</v>
       </c>
       <c r="H3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I3" t="n">
         <v>1</v>
       </c>
       <c r="J3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
@@ -798,83 +798,83 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>1.18</v>
+        <v>1.76</v>
       </c>
       <c r="M3" t="n">
-        <v>6.96</v>
+        <v>3.73</v>
       </c>
       <c r="N3" t="n">
-        <v>10.23</v>
+        <v>4.09</v>
       </c>
       <c r="O3" t="n">
-        <v>1.54</v>
+        <v>2.2</v>
       </c>
       <c r="P3" t="n">
-        <v>2.85</v>
+        <v>2.24</v>
       </c>
       <c r="Q3" t="n">
-        <v>8.4</v>
+        <v>4.6</v>
       </c>
       <c r="R3" t="n">
-        <v>1.19</v>
+        <v>1.32</v>
       </c>
       <c r="S3" t="n">
-        <v>4.2</v>
+        <v>3.1</v>
       </c>
       <c r="T3" t="n">
-        <v>2.01</v>
+        <v>2.53</v>
       </c>
       <c r="U3" t="n">
-        <v>1.73</v>
+        <v>1.46</v>
       </c>
       <c r="V3" t="n">
         <v>1.01</v>
       </c>
       <c r="W3" t="n">
-        <v>1.06</v>
+        <v>1.18</v>
       </c>
       <c r="X3" t="n">
-        <v>6.2</v>
+        <v>3.82</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.4</v>
+        <v>1.68</v>
       </c>
       <c r="Z3" t="n">
-        <v>2.73</v>
+        <v>2.05</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.97</v>
+        <v>2.7</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.78</v>
+        <v>1.36</v>
       </c>
       <c r="AC3" t="n">
-        <v>1.89</v>
+        <v>1.68</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.82</v>
+        <v>2.01</v>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>['26']</t>
+          <t>['39']</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>['22', '49']</t>
+          <t>['69']</t>
         </is>
       </c>
       <c r="AG3" t="n">
-        <v>1.04</v>
+        <v>1.14</v>
       </c>
       <c r="AH3" t="n">
-        <v>3.1</v>
+        <v>2.02</v>
       </c>
       <c r="AI3" t="n">
-        <v>1.18</v>
+        <v>1.5</v>
       </c>
       <c r="AJ3" t="n">
-        <v>4.4</v>
+        <v>2.65</v>
       </c>
       <c r="AK3" s="3" t="n">
         <v>45672.33333333334</v>
@@ -901,25 +901,25 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Prachuap</t>
+          <t>Port FC</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Sukhothai</t>
+          <t>Khon Kaen United</t>
         </is>
       </c>
       <c r="G4" t="n">
         <v>1</v>
       </c>
       <c r="H4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I4" t="n">
         <v>1</v>
       </c>
       <c r="J4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
@@ -927,83 +927,83 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>1.76</v>
+        <v>1.18</v>
       </c>
       <c r="M4" t="n">
-        <v>3.73</v>
+        <v>6.96</v>
       </c>
       <c r="N4" t="n">
-        <v>4.09</v>
+        <v>10.23</v>
       </c>
       <c r="O4" t="n">
-        <v>2.2</v>
+        <v>1.54</v>
       </c>
       <c r="P4" t="n">
-        <v>2.24</v>
+        <v>2.85</v>
       </c>
       <c r="Q4" t="n">
-        <v>4.6</v>
+        <v>8.4</v>
       </c>
       <c r="R4" t="n">
-        <v>1.32</v>
+        <v>1.19</v>
       </c>
       <c r="S4" t="n">
-        <v>3.1</v>
+        <v>4.2</v>
       </c>
       <c r="T4" t="n">
-        <v>2.53</v>
+        <v>2.01</v>
       </c>
       <c r="U4" t="n">
-        <v>1.46</v>
+        <v>1.73</v>
       </c>
       <c r="V4" t="n">
         <v>1.01</v>
       </c>
       <c r="W4" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="X4" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AE4" t="inlineStr">
+        <is>
+          <t>['26']</t>
+        </is>
+      </c>
+      <c r="AF4" t="inlineStr">
+        <is>
+          <t>['22', '49']</t>
+        </is>
+      </c>
+      <c r="AG4" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AI4" t="n">
         <v>1.18</v>
       </c>
-      <c r="X4" t="n">
-        <v>3.82</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AA4" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="AD4" t="n">
-        <v>2.01</v>
-      </c>
-      <c r="AE4" t="inlineStr">
-        <is>
-          <t>['39']</t>
-        </is>
-      </c>
-      <c r="AF4" t="inlineStr">
-        <is>
-          <t>['69']</t>
-        </is>
-      </c>
-      <c r="AG4" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="AH4" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="AI4" t="n">
-        <v>1.5</v>
-      </c>
       <c r="AJ4" t="n">
-        <v>2.65</v>
+        <v>4.4</v>
       </c>
       <c r="AK4" s="3" t="n">
         <v>45672.33333333334</v>
@@ -1030,22 +1030,22 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Buriram United</t>
+          <t>Bangkok Glass</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Chiangrai United</t>
+          <t>Ratchaburi</t>
         </is>
       </c>
       <c r="G5" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="H5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I5" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
@@ -1056,83 +1056,83 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>1.07</v>
+        <v>1.7</v>
       </c>
       <c r="M5" t="n">
-        <v>11.68</v>
+        <v>3.81</v>
       </c>
       <c r="N5" t="n">
-        <v>18.58</v>
+        <v>4.27</v>
       </c>
       <c r="O5" t="n">
-        <v>1.38</v>
+        <v>2.22</v>
       </c>
       <c r="P5" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="R5" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="S5" t="n">
         <v>3.1</v>
       </c>
-      <c r="Q5" t="n">
-        <v>13</v>
-      </c>
-      <c r="R5" t="n">
+      <c r="T5" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="U5" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="V5" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="W5" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="X5" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="AE5" t="inlineStr">
+        <is>
+          <t>['69']</t>
+        </is>
+      </c>
+      <c r="AF5" t="inlineStr">
+        <is>
+          <t>['63', '67']</t>
+        </is>
+      </c>
+      <c r="AG5" t="n">
         <v>1.18</v>
       </c>
-      <c r="S5" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="T5" t="n">
-        <v>1.97</v>
-      </c>
-      <c r="U5" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="V5" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W5" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="X5" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>2.43</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AE5" t="inlineStr">
-        <is>
-          <t>['5', '21', '23', '29', '35', '73', '76', '90+1']</t>
-        </is>
-      </c>
-      <c r="AF5" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG5" t="n">
-        <v>1.01</v>
-      </c>
       <c r="AH5" t="n">
-        <v>3.95</v>
+        <v>1.83</v>
       </c>
       <c r="AI5" t="n">
-        <v>1.11</v>
+        <v>1.53</v>
       </c>
       <c r="AJ5" t="n">
-        <v>5.65</v>
+        <v>2.57</v>
       </c>
       <c r="AK5" s="3" t="n">
         <v>45672.375</v>
@@ -1159,22 +1159,22 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Bangkok Glass</t>
+          <t>Buriram United</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ratchaburi</t>
+          <t>Chiangrai United</t>
         </is>
       </c>
       <c r="G6" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="H6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I6" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
@@ -1185,83 +1185,83 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>1.7</v>
+        <v>1.07</v>
       </c>
       <c r="M6" t="n">
-        <v>3.81</v>
+        <v>11.68</v>
       </c>
       <c r="N6" t="n">
-        <v>4.27</v>
+        <v>18.58</v>
       </c>
       <c r="O6" t="n">
-        <v>2.22</v>
+        <v>1.38</v>
       </c>
       <c r="P6" t="n">
-        <v>2.24</v>
+        <v>3.1</v>
       </c>
       <c r="Q6" t="n">
-        <v>4.5</v>
+        <v>13</v>
       </c>
       <c r="R6" t="n">
-        <v>1.32</v>
+        <v>1.18</v>
       </c>
       <c r="S6" t="n">
-        <v>3.1</v>
+        <v>4.3</v>
       </c>
       <c r="T6" t="n">
-        <v>2.5</v>
+        <v>1.97</v>
       </c>
       <c r="U6" t="n">
-        <v>1.48</v>
+        <v>1.76</v>
       </c>
       <c r="V6" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="W6" t="n">
-        <v>1.22</v>
+        <v>1.08</v>
       </c>
       <c r="X6" t="n">
-        <v>3.9</v>
+        <v>5.5</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.68</v>
+        <v>1.33</v>
       </c>
       <c r="Z6" t="n">
-        <v>2.05</v>
+        <v>3.05</v>
       </c>
       <c r="AA6" t="n">
-        <v>2.7</v>
+        <v>1.89</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.41</v>
+        <v>1.85</v>
       </c>
       <c r="AC6" t="n">
-        <v>1.69</v>
+        <v>2.43</v>
       </c>
       <c r="AD6" t="n">
-        <v>2.04</v>
+        <v>1.5</v>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>['69']</t>
+          <t>['5', '21', '23', '29', '35', '73', '76', '90+1']</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>['63', '67']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AG6" t="n">
-        <v>1.18</v>
+        <v>1.01</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.83</v>
+        <v>3.95</v>
       </c>
       <c r="AI6" t="n">
-        <v>1.53</v>
+        <v>1.11</v>
       </c>
       <c r="AJ6" t="n">
-        <v>2.57</v>
+        <v>5.65</v>
       </c>
       <c r="AK6" s="3" t="n">
         <v>45672.375</v>
@@ -2320,25 +2320,25 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Stuttgart</t>
+          <t>Union Berlin</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>RB Leipzig</t>
+          <t>Augsburg</t>
         </is>
       </c>
       <c r="G15" t="n">
+        <v>0</v>
+      </c>
+      <c r="H15" t="n">
         <v>2</v>
       </c>
-      <c r="H15" t="n">
-        <v>1</v>
-      </c>
       <c r="I15" t="n">
         <v>0</v>
       </c>
       <c r="J15" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K15" t="inlineStr">
         <is>
@@ -2346,83 +2346,83 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>1.95</v>
+        <v>1.88</v>
       </c>
       <c r="M15" t="n">
-        <v>3.58</v>
+        <v>3.14</v>
       </c>
       <c r="N15" t="n">
-        <v>2.96</v>
+        <v>3.59</v>
       </c>
       <c r="O15" t="n">
         <v>2.6</v>
       </c>
       <c r="P15" t="n">
-        <v>2.5</v>
+        <v>2.1</v>
       </c>
       <c r="Q15" t="n">
-        <v>3.4</v>
+        <v>4.75</v>
       </c>
       <c r="R15" t="n">
-        <v>1.25</v>
+        <v>1.44</v>
       </c>
       <c r="S15" t="n">
-        <v>3.75</v>
+        <v>2.63</v>
       </c>
       <c r="T15" t="n">
-        <v>2.2</v>
+        <v>3.25</v>
       </c>
       <c r="U15" t="n">
-        <v>1.62</v>
+        <v>1.33</v>
       </c>
       <c r="V15" t="n">
-        <v>1.02</v>
+        <v>1.07</v>
       </c>
       <c r="W15" t="n">
-        <v>1.15</v>
+        <v>1.38</v>
       </c>
       <c r="X15" t="n">
-        <v>5.5</v>
+        <v>3.1</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.44</v>
+        <v>2.05</v>
       </c>
       <c r="Z15" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>4</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AE15" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF15" t="inlineStr">
+        <is>
+          <t>['8', '30']</t>
+        </is>
+      </c>
+      <c r="AG15" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AH15" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AI15" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AJ15" t="n">
         <v>2.75</v>
-      </c>
-      <c r="AA15" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="AB15" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="AC15" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AD15" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="AE15" t="inlineStr">
-        <is>
-          <t>['50', '60']</t>
-        </is>
-      </c>
-      <c r="AF15" t="inlineStr">
-        <is>
-          <t>['10']</t>
-        </is>
-      </c>
-      <c r="AG15" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AH15" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="AI15" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AJ15" t="n">
-        <v>2.2</v>
       </c>
       <c r="AK15" s="3" t="n">
         <v>45672.6875</v>
@@ -2578,109 +2578,109 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Union Berlin</t>
+          <t>Bayern München</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Augsburg</t>
+          <t>Hoffenheim</t>
         </is>
       </c>
       <c r="G17" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I17" t="n">
+        <v>3</v>
+      </c>
+      <c r="J17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="L17" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="M17" t="n">
+        <v>7.53</v>
+      </c>
+      <c r="N17" t="n">
+        <v>11.56</v>
+      </c>
+      <c r="O17" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="P17" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>10</v>
+      </c>
+      <c r="R17" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="S17" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="T17" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="U17" t="n">
         <v>2</v>
       </c>
-      <c r="I17" t="n">
-        <v>0</v>
-      </c>
-      <c r="J17" t="n">
+      <c r="V17" t="n">
+        <v>0</v>
+      </c>
+      <c r="W17" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="X17" t="n">
+        <v>10</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AD17" t="n">
         <v>2</v>
       </c>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="L17" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="M17" t="n">
-        <v>3.14</v>
-      </c>
-      <c r="N17" t="n">
-        <v>3.59</v>
-      </c>
-      <c r="O17" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="P17" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="R17" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="S17" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="T17" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="U17" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="V17" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="W17" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="X17" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="Y17" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AA17" t="n">
-        <v>4</v>
-      </c>
-      <c r="AB17" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="AC17" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AD17" t="n">
-        <v>1.8</v>
-      </c>
       <c r="AE17" t="inlineStr">
         <is>
+          <t>['6', '12', '26', '48', '66']</t>
+        </is>
+      </c>
+      <c r="AF17" t="inlineStr">
+        <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="AF17" t="inlineStr">
-        <is>
-          <t>['8', '30']</t>
-        </is>
-      </c>
       <c r="AG17" t="n">
-        <v>1.21</v>
+        <v>1.02</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.87</v>
+        <v>6</v>
       </c>
       <c r="AI17" t="n">
-        <v>1.57</v>
+        <v>1.18</v>
       </c>
       <c r="AJ17" t="n">
-        <v>2.75</v>
+        <v>4.5</v>
       </c>
       <c r="AK17" s="3" t="n">
         <v>45672.6875</v>
@@ -2697,7 +2697,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2707,91 +2707,91 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Bayern München</t>
+          <t>Newcastle United</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Hoffenheim</t>
+          <t>Wolverhampton Wanderers</t>
         </is>
       </c>
       <c r="G18" t="n">
+        <v>3</v>
+      </c>
+      <c r="H18" t="n">
+        <v>0</v>
+      </c>
+      <c r="I18" t="n">
+        <v>1</v>
+      </c>
+      <c r="J18" t="n">
+        <v>0</v>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="L18" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="M18" t="n">
+        <v>4.18</v>
+      </c>
+      <c r="N18" t="n">
         <v>5</v>
       </c>
-      <c r="H18" t="n">
-        <v>0</v>
-      </c>
-      <c r="I18" t="n">
-        <v>3</v>
-      </c>
-      <c r="J18" t="n">
-        <v>0</v>
-      </c>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="L18" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="M18" t="n">
-        <v>7.53</v>
-      </c>
-      <c r="N18" t="n">
-        <v>11.56</v>
-      </c>
       <c r="O18" t="n">
-        <v>1.44</v>
+        <v>1.8</v>
       </c>
       <c r="P18" t="n">
-        <v>3.5</v>
+        <v>2.75</v>
       </c>
       <c r="Q18" t="n">
-        <v>10</v>
+        <v>6.5</v>
       </c>
       <c r="R18" t="n">
-        <v>1.14</v>
+        <v>1.22</v>
       </c>
       <c r="S18" t="n">
-        <v>5.5</v>
+        <v>4</v>
       </c>
       <c r="T18" t="n">
-        <v>1.73</v>
+        <v>2.1</v>
       </c>
       <c r="U18" t="n">
-        <v>2</v>
+        <v>1.67</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W18" t="n">
-        <v>1.05</v>
+        <v>1.13</v>
       </c>
       <c r="X18" t="n">
-        <v>10</v>
+        <v>6.4</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.22</v>
+        <v>1.45</v>
       </c>
       <c r="Z18" t="n">
-        <v>4.2</v>
+        <v>2.7</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.74</v>
+        <v>2.1</v>
       </c>
       <c r="AB18" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AD18" t="n">
         <v>2.1</v>
       </c>
-      <c r="AC18" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AD18" t="n">
-        <v>2</v>
-      </c>
       <c r="AE18" t="inlineStr">
         <is>
-          <t>['6', '12', '26', '48', '66']</t>
+          <t>['34', '57', '74']</t>
         </is>
       </c>
       <c r="AF18" t="inlineStr">
@@ -2800,16 +2800,16 @@
         </is>
       </c>
       <c r="AG18" t="n">
-        <v>1.02</v>
+        <v>1.09</v>
       </c>
       <c r="AH18" t="n">
-        <v>6</v>
+        <v>3.1</v>
       </c>
       <c r="AI18" t="n">
-        <v>1.18</v>
+        <v>1.25</v>
       </c>
       <c r="AJ18" t="n">
-        <v>4.5</v>
+        <v>3.75</v>
       </c>
       <c r="AK18" s="3" t="n">
         <v>45672.6875</v>
@@ -2826,7 +2826,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2836,109 +2836,109 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Newcastle United</t>
+          <t>Stuttgart</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Wolverhampton Wanderers</t>
+          <t>RB Leipzig</t>
         </is>
       </c>
       <c r="G19" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I19" t="n">
+        <v>0</v>
+      </c>
+      <c r="J19" t="n">
         <v>1</v>
       </c>
-      <c r="J19" t="n">
-        <v>0</v>
-      </c>
       <c r="K19" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
       </c>
       <c r="L19" t="n">
-        <v>1.51</v>
+        <v>1.95</v>
       </c>
       <c r="M19" t="n">
-        <v>4.18</v>
+        <v>3.58</v>
       </c>
       <c r="N19" t="n">
-        <v>5</v>
+        <v>2.96</v>
       </c>
       <c r="O19" t="n">
-        <v>1.8</v>
+        <v>2.6</v>
       </c>
       <c r="P19" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="R19" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="S19" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="T19" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="U19" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="V19" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="W19" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="X19" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="Z19" t="n">
         <v>2.75</v>
       </c>
-      <c r="Q19" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="R19" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="S19" t="n">
-        <v>4</v>
-      </c>
-      <c r="T19" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="U19" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="V19" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W19" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="X19" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="Y19" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="Z19" t="n">
-        <v>2.7</v>
-      </c>
       <c r="AA19" t="n">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.71</v>
+        <v>1.68</v>
       </c>
       <c r="AC19" t="n">
-        <v>1.67</v>
+        <v>1.44</v>
       </c>
       <c r="AD19" t="n">
-        <v>2.1</v>
+        <v>2.63</v>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
-          <t>['34', '57', '74']</t>
+          <t>['50', '60']</t>
         </is>
       </c>
       <c r="AF19" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['10']</t>
         </is>
       </c>
       <c r="AG19" t="n">
-        <v>1.09</v>
+        <v>1.36</v>
       </c>
       <c r="AH19" t="n">
-        <v>3.1</v>
+        <v>1.68</v>
       </c>
       <c r="AI19" t="n">
-        <v>1.25</v>
+        <v>1.62</v>
       </c>
       <c r="AJ19" t="n">
-        <v>3.75</v>
+        <v>2.2</v>
       </c>
       <c r="AK19" s="3" t="n">
         <v>45672.6875</v>
@@ -3213,7 +3213,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3223,25 +3223,25 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Inter Milan</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Portsmouth</t>
         </is>
       </c>
       <c r="G22" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H22" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I22" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K22" t="inlineStr">
         <is>
@@ -3249,83 +3249,83 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>1.37</v>
+        <v>1.71</v>
       </c>
       <c r="M22" t="n">
-        <v>4.18</v>
+        <v>3.46</v>
       </c>
       <c r="N22" t="n">
-        <v>6.47</v>
+        <v>4.36</v>
       </c>
       <c r="O22" t="n">
-        <v>1.95</v>
+        <v>2.25</v>
       </c>
       <c r="P22" t="n">
-        <v>2.38</v>
+        <v>2.25</v>
       </c>
       <c r="Q22" t="n">
-        <v>6.5</v>
+        <v>5</v>
       </c>
       <c r="R22" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="S22" t="n">
-        <v>3.25</v>
+        <v>3</v>
       </c>
       <c r="T22" t="n">
-        <v>2.63</v>
+        <v>2.75</v>
       </c>
       <c r="U22" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="V22" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="W22" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="X22" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AE22" t="inlineStr">
+        <is>
+          <t>['61', '71', '76']</t>
+        </is>
+      </c>
+      <c r="AF22" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG22" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AH22" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AI22" t="n">
         <v>1.44</v>
       </c>
-      <c r="V22" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="W22" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="X22" t="n">
-        <v>4</v>
-      </c>
-      <c r="Y22" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="Z22" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AA22" t="n">
+      <c r="AJ22" t="n">
         <v>3</v>
-      </c>
-      <c r="AB22" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AC22" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AD22" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AE22" t="inlineStr">
-        <is>
-          <t>['19', '45+1']</t>
-        </is>
-      </c>
-      <c r="AF22" t="inlineStr">
-        <is>
-          <t>['15', '64']</t>
-        </is>
-      </c>
-      <c r="AG22" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AH22" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="AI22" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AJ22" t="n">
-        <v>3.75</v>
       </c>
       <c r="AK22" s="3" t="n">
         <v>45672.69791666666</v>
@@ -3342,7 +3342,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3352,109 +3352,109 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Inter Milan</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Portsmouth</t>
+          <t>Bologna</t>
         </is>
       </c>
       <c r="G23" t="n">
+        <v>2</v>
+      </c>
+      <c r="H23" t="n">
+        <v>2</v>
+      </c>
+      <c r="I23" t="n">
+        <v>2</v>
+      </c>
+      <c r="J23" t="n">
+        <v>1</v>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="L23" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="M23" t="n">
+        <v>4.18</v>
+      </c>
+      <c r="N23" t="n">
+        <v>6.47</v>
+      </c>
+      <c r="O23" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="P23" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="R23" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="S23" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="T23" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="U23" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="V23" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="W23" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="X23" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AA23" t="n">
         <v>3</v>
       </c>
-      <c r="H23" t="n">
-        <v>0</v>
-      </c>
-      <c r="I23" t="n">
-        <v>0</v>
-      </c>
-      <c r="J23" t="n">
-        <v>0</v>
-      </c>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="L23" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="M23" t="n">
-        <v>3.46</v>
-      </c>
-      <c r="N23" t="n">
-        <v>4.36</v>
-      </c>
-      <c r="O23" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="P23" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="Q23" t="n">
-        <v>5</v>
-      </c>
-      <c r="R23" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="S23" t="n">
-        <v>3</v>
-      </c>
-      <c r="T23" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="U23" t="n">
+      <c r="AB23" t="n">
         <v>1.4</v>
       </c>
-      <c r="V23" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="W23" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="X23" t="n">
+      <c r="AC23" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AE23" t="inlineStr">
+        <is>
+          <t>['19', '45+1']</t>
+        </is>
+      </c>
+      <c r="AF23" t="inlineStr">
+        <is>
+          <t>['15', '64']</t>
+        </is>
+      </c>
+      <c r="AG23" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AH23" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="AI23" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AJ23" t="n">
         <v>3.75</v>
-      </c>
-      <c r="Y23" t="n">
-        <v>2.01</v>
-      </c>
-      <c r="Z23" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AA23" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AB23" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AC23" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AD23" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AE23" t="inlineStr">
-        <is>
-          <t>['61', '71', '76']</t>
-        </is>
-      </c>
-      <c r="AF23" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG23" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AH23" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AI23" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AJ23" t="n">
-        <v>3</v>
       </c>
       <c r="AK23" s="3" t="n">
         <v>45672.69791666666</v>
@@ -3471,7 +3471,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3481,109 +3481,109 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Aberdeen</t>
+          <t>Tottenham Hotspur</t>
         </is>
       </c>
       <c r="G24" t="n">
+        <v>2</v>
+      </c>
+      <c r="H24" t="n">
+        <v>1</v>
+      </c>
+      <c r="I24" t="n">
+        <v>2</v>
+      </c>
+      <c r="J24" t="n">
+        <v>1</v>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="L24" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="M24" t="n">
+        <v>4.27</v>
+      </c>
+      <c r="N24" t="n">
+        <v>5</v>
+      </c>
+      <c r="O24" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="P24" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>6</v>
+      </c>
+      <c r="R24" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="S24" t="n">
+        <v>4</v>
+      </c>
+      <c r="T24" t="n">
+        <v>2</v>
+      </c>
+      <c r="U24" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="V24" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W24" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="X24" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AE24" t="inlineStr">
+        <is>
+          <t>['40', '44']</t>
+        </is>
+      </c>
+      <c r="AF24" t="inlineStr">
+        <is>
+          <t>['25']</t>
+        </is>
+      </c>
+      <c r="AG24" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AH24" t="n">
         <v>3</v>
-      </c>
-      <c r="H24" t="n">
-        <v>0</v>
-      </c>
-      <c r="I24" t="n">
-        <v>1</v>
-      </c>
-      <c r="J24" t="n">
-        <v>0</v>
-      </c>
-      <c r="K24" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="L24" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="M24" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="N24" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="O24" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="P24" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="Q24" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="R24" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="S24" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="T24" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="U24" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="V24" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="W24" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="X24" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="Y24" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="Z24" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="AA24" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="AB24" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="AC24" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AD24" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AE24" t="inlineStr">
-        <is>
-          <t>['13', '90+3', '90+7']</t>
-        </is>
-      </c>
-      <c r="AF24" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG24" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="AH24" t="n">
-        <v>3.7</v>
       </c>
       <c r="AI24" t="n">
         <v>1.29</v>
       </c>
       <c r="AJ24" t="n">
-        <v>3.75</v>
+        <v>3.5</v>
       </c>
       <c r="AK24" s="3" t="n">
         <v>45672.70833333334</v>
@@ -3600,7 +3600,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3610,25 +3610,25 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur</t>
+          <t>Aberdeen</t>
         </is>
       </c>
       <c r="G25" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H25" t="n">
+        <v>0</v>
+      </c>
+      <c r="I25" t="n">
         <v>1</v>
       </c>
-      <c r="I25" t="n">
-        <v>2</v>
-      </c>
       <c r="J25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K25" t="inlineStr">
         <is>
@@ -3636,83 +3636,83 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>1.49</v>
+        <v>1.25</v>
       </c>
       <c r="M25" t="n">
-        <v>4.27</v>
+        <v>5.3</v>
       </c>
       <c r="N25" t="n">
-        <v>5</v>
+        <v>7.4</v>
       </c>
       <c r="O25" t="n">
-        <v>1.8</v>
+        <v>1.91</v>
       </c>
       <c r="P25" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="R25" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="S25" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="T25" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="U25" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="V25" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="W25" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="X25" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="Z25" t="n">
         <v>2.75</v>
       </c>
-      <c r="Q25" t="n">
-        <v>6</v>
-      </c>
-      <c r="R25" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="S25" t="n">
-        <v>4</v>
-      </c>
-      <c r="T25" t="n">
-        <v>2</v>
-      </c>
-      <c r="U25" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="V25" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W25" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="X25" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="Y25" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="Z25" t="n">
-        <v>3.1</v>
-      </c>
       <c r="AA25" t="n">
-        <v>1.98</v>
+        <v>2.23</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.81</v>
+        <v>1.61</v>
       </c>
       <c r="AC25" t="n">
-        <v>1.62</v>
+        <v>1.91</v>
       </c>
       <c r="AD25" t="n">
-        <v>2.2</v>
+        <v>1.91</v>
       </c>
       <c r="AE25" t="inlineStr">
         <is>
-          <t>['40', '44']</t>
+          <t>['13', '90+3', '90+7']</t>
         </is>
       </c>
       <c r="AF25" t="inlineStr">
         <is>
-          <t>['25']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AG25" t="n">
-        <v>1.1</v>
+        <v>1.04</v>
       </c>
       <c r="AH25" t="n">
-        <v>3</v>
+        <v>3.7</v>
       </c>
       <c r="AI25" t="n">
         <v>1.29</v>
       </c>
       <c r="AJ25" t="n">
-        <v>3.5</v>
+        <v>3.75</v>
       </c>
       <c r="AK25" s="3" t="n">
         <v>45672.70833333334</v>
